--- a/reports/Debug-purgatory-20260105/Month to Date (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260105/Month to Date (Actual)_Budget.xlsx
@@ -19,15 +19,84 @@
     <t>Department</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5205</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>99150</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
     <t>D6780</t>
   </si>
   <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -52,39 +121,6 @@
     <t>D6800</t>
   </si>
   <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D4053</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5205</t>
-  </si>
-  <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>D6710</t>
-  </si>
-  <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
     <t>99100</t>
   </si>
   <si>
@@ -121,51 +157,15 @@
     <t>D5810</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D6212</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>99150</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8030</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Payroll</t>
+  </si>
+  <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>Payroll</t>
-  </si>
-  <si>
     <t>Visits</t>
   </si>
   <si>
@@ -175,15 +175,84 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>Lift Maintenance</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Expert Edge</t>
+  </si>
+  <si>
+    <t>Purg Sports Main Ave</t>
+  </si>
+  <si>
+    <t>Waffle Cabin</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Comp Tickets</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
+  </si>
+  <si>
+    <t>F&amp;B Admin</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
     <t>Mountain G&amp;A</t>
   </si>
   <si>
@@ -208,39 +277,6 @@
     <t>Commercial Tenants</t>
   </si>
   <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>Expert Edge</t>
-  </si>
-  <si>
-    <t>Purg Sports Main Ave</t>
-  </si>
-  <si>
-    <t>Waffle Cabin</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>Accounting/Mgmt Services</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>IT Services</t>
-  </si>
-  <si>
     <t>Daily Winter Ticketed</t>
   </si>
   <si>
@@ -275,42 +311,6 @@
   </si>
   <si>
     <t>Events</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
-  </si>
-  <si>
-    <t>Functions</t>
-  </si>
-  <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
-  </si>
-  <si>
-    <t>Comp Tickets</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>F&amp;B Admin</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>General Administration</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>HR</t>
   </si>
 </sst>
 </file>
@@ -704,7 +704,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="2">
-        <v>2523.55</v>
+        <v>10296.63</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>53</v>
@@ -712,44 +712,44 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
-        <v>12990.50</v>
+        <v>11677.16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2">
-        <v>10234.00</v>
+        <v>2971.85</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>1136.05</v>
+        <v>463374.10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -757,10 +757,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2">
-        <v>1729.95</v>
+        <v>8822.58</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>56</v>
@@ -771,10 +771,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2">
-        <v>3032.78</v>
+        <v>2761.31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>57</v>
@@ -785,10 +785,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2">
-        <v>106334.53</v>
+        <v>0.00</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>57</v>
@@ -799,10 +799,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
-        <v>2641.50</v>
+        <v>29323.85</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>58</v>
@@ -810,156 +810,156 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="2">
-        <v>10943.15</v>
+        <v>3667.90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2">
-        <v>2113.49</v>
+        <v>23686.26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="2">
-        <v>3600.60</v>
+        <v>6902.99</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="2">
-        <v>1956.85</v>
+        <v>1376599.82</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="2">
-        <v>9791.20</v>
+        <v>3025.78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>947.10</v>
+        <v>22365.99</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>1106.25</v>
+        <v>31659.40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>7975.25</v>
+        <v>3941.28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="2">
-        <v>4316.40</v>
+        <v>1131.95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>0.00</v>
+        <v>9022.35</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>29323.85</v>
+        <v>7160.70</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -970,7 +970,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>3667.90</v>
+        <v>39388.92</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>65</v>
@@ -981,10 +981,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>23686.26</v>
+        <v>5953.15</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>66</v>
@@ -992,16 +992,16 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>6902.99</v>
+        <v>8727.25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1012,7 +1012,7 @@
         <v>48</v>
       </c>
       <c r="C24" s="2">
-        <v>1376599.82</v>
+        <v>5597.85</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>67</v>
@@ -1020,16 +1020,16 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>3025.78</v>
+        <v>8178.95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1040,7 +1040,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="2">
-        <v>22365.99</v>
+        <v>3934.98</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>68</v>
@@ -1051,10 +1051,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="2">
-        <v>31659.40</v>
+        <v>2595.00</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>69</v>
@@ -1062,618 +1062,618 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2">
-        <v>3941.28</v>
+        <v>5316.69</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="2">
-        <v>1131.95</v>
+        <v>5330.55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C30" s="2">
-        <v>9022.35</v>
+        <v>4747.24</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="2">
-        <v>7160.70</v>
+        <v>42236.05</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>39388.92</v>
+        <v>1605.60</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2">
-        <v>5953.15</v>
+        <v>6142.05</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C34" s="2">
-        <v>8727.25</v>
+        <v>3868.95</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2">
-        <v>5597.85</v>
+        <v>10234.00</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C36" s="2">
-        <v>8178.95</v>
+        <v>1136.05</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>3934.98</v>
+        <v>2523.55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>8472.00</v>
+        <v>12990.50</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2">
-        <v>43847.49</v>
+        <v>1729.95</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C40" s="2">
-        <v>224789.00</v>
+        <v>3032.78</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>2339.85</v>
+        <v>106334.53</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C42" s="2">
-        <v>5751.27</v>
+        <v>2641.50</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>215612.40</v>
+        <v>10943.15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>11548.30</v>
+        <v>2113.49</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>61420.36</v>
+        <v>3600.60</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="2">
-        <v>13226.35</v>
+        <v>1956.85</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>20036.25</v>
+        <v>9791.20</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>1965.60</v>
+        <v>947.10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>3635.07</v>
+        <v>1106.25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2">
-        <v>3746.76</v>
+        <v>7975.25</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="2">
-        <v>7659.10</v>
+        <v>4316.40</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2">
-        <v>38171.30</v>
+        <v>0.00</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" s="2">
-        <v>1218.75</v>
+        <v>8472.00</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="2">
-        <v>17849.10</v>
+        <v>43847.49</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2">
-        <v>117574.79</v>
+        <v>224789.00</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" s="2">
-        <v>1006.25</v>
+        <v>2339.85</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>0.00</v>
+        <v>5751.27</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="2">
-        <v>10296.63</v>
+        <v>215612.40</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C59" s="2">
-        <v>11677.16</v>
+        <v>11548.30</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C60" s="2">
-        <v>2971.85</v>
+        <v>61420.36</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="2">
-        <v>463374.10</v>
+        <v>13226.35</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="2">
-        <v>8822.58</v>
+        <v>20036.25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2">
-        <v>2761.31</v>
+        <v>1965.60</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C64" s="2">
-        <v>0.00</v>
+        <v>3635.07</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C65" s="2">
-        <v>2595.00</v>
+        <v>3746.76</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C66" s="2">
-        <v>5316.69</v>
+        <v>7659.10</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C67" s="2">
-        <v>5330.55</v>
+        <v>38171.30</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C68" s="2">
-        <v>4747.24</v>
+        <v>1218.75</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C69" s="2">
-        <v>42236.05</v>
+        <v>17849.10</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70" s="2">
-        <v>1605.60</v>
+        <v>117574.79</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C71" s="2">
-        <v>6142.05</v>
+        <v>1006.25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1684,7 +1684,7 @@
         <v>49</v>
       </c>
       <c r="C72" s="2">
-        <v>3868.95</v>
+        <v>0.00</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
